--- a/docs/chemical-build/deliverables/used-chemical-process-plants-for-sale-brief-simple.xlsx
+++ b/docs/chemical-build/deliverables/used-chemical-process-plants-for-sale-brief-simple.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -432,9 +432,9 @@
     <col width="39" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -529,13 +529,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optimize the existing chemical page for buyers first, with a supporting seller section. Preserve existing URL and seven categories.</t>
+          <t>Two-sided commercial collection page on the existing URL. Buyers find, inspect and acquire used chemical plants and equipment; plant owners sell shutdown plants and surplus equipment to IPP. Content arrangement follows the live reactor hub: hero triples, browse by type, listings, makers, advantages, process, industries, FAQ, call to action.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>used chemical process plants for sale</t>
         </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>international process plants</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -545,36 +555,309 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>used chemical plant equipment</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ipp equipment</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>used chemical plant equipment</t>
+          <t>used chemical equipment</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>chemical process equipment for sale</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ipp used equipment</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>chemical process equipment for sale</t>
+          <t>used chemical process equipment</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sell chemical plant</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>used chemical processing equipment</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>sell used chemical equipment</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>second hand chemical equipment</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>sell batch chemical plant</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>used chemical plants for sale</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>chemical plant decommissioning</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>chemical plants for sale</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>used chemical plants</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>used chemical machinery</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>buy chemical processing equipment</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>best marketplace for used chemical processing equipment</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>how can i find second-hand chemical processing plants for sale</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -587,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -679,14 +962,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Primary entity and preserved equipment-led introduction</t>
-        </is>
-      </c>
+          <t>Hero for a two-sided collection page. Sentence 1 stays word for word because AI answers quote it, with the first mention spelled out as International Process Plants (IPP). Sentence 2 is the buyer opener in IPP form with the establishes and sidelining verbs. Sentence 3 states the seller side: plant owners turn shutdown plants and surplus equipment into capital through IPP. A stat strip carries 15,000+ inventory items, 20 complete plant sites, offices in 15 countries and since 1980. Three cards route to complete plants, equipment and surplus assets.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>used chemical process plants for sale</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,14 +992,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Six client logos featured on the IPP homepage; no invented rating</t>
-        </is>
-      </c>
+          <t>Logo row of six customers featured on the IPP homepage: Shell, Sanofi, Lilly, Dow, Lonza and Air Products, with a source note.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>used chemical plant equipment</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -723,14 +1022,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Retain company description, published inventory footprint with date and source</t>
-        </is>
-      </c>
+          <t>Company description that AI Mode repeats, kept word for word, with the as-of date and source on the company-wide figures. One added statement names both roles: IPP acquires plants, process lines and surplus equipment from restructuring producers and resells or redeploys them worldwide.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>chemical process equipment for sale</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -745,9 +1052,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Selected verified IMS listings; type, capacity, material, condition, location and stock numbers; no location filter</t>
-        </is>
-      </c>
+          <t>Listing grid of selected IMS records with filters: six complete plants with capacity, technology, feedstock and location; eight equipment units with material, condition, pressure and temperature. Stock-number search and an empty state route to the full IMS inventory.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -762,128 +1078,200 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve original seven categories and descriptions; link each hub and IMS search</t>
-        </is>
-      </c>
+          <t>Seven equipment types in their original order. Each type card keeps the original description sentence and adds separate statements for the makers from the IMS manufacturer filters, the materials of construction, the size range from the IMS sliders in metric with imperial in brackets, and the featured stock number.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equipment manufacturers in our inventory</t>
+          <t>Reactors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Manufacturers verified on exact IMS detail pages; scope to featured listings</t>
-        </is>
-      </c>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why chemical manufacturers choose IPP for chemical process plants</t>
+          <t>Heat exchangers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve five existing benefit labels; source supported values; no generic savings promise</t>
-        </is>
-      </c>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What do chemical manufacturers say about IPP? Reviews</t>
+          <t>Centrifuges</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Link real company customer video playlist; no invented quote or aggregate rating; distinguish general customer stories</t>
-        </is>
-      </c>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How buying from IPP works</t>
+          <t>Dryers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Specifications and photos; inspection; purchase; dismantling/relocation; shipping; start-up scope; financing</t>
-        </is>
-      </c>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Industries we serve</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve six original sectors verbatim as a bare list</t>
-        </is>
-      </c>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sell chemical plants and surplus equipment to IPP</t>
+          <t>Distillation columns</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Complete plants, lines and equipment; valuation, decommissioning, dismantling, global marketing; two seller form destinations</t>
-        </is>
-      </c>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Global inventory. Local support.</t>
+          <t>Tanks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Published warehouses in Eastover, Billingham, Bitterfeld; offices; no location filter</t>
-        </is>
-      </c>
+          <t>Type card: original description sentence; makers in IPP inventory; materials of construction; size range in metric with imperial; featured listing.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -893,65 +1281,1531 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chemical plant projects and industry recognition</t>
+          <t>Equipment manufacturers in our inventory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. BASF, Novartis, CDMO, SOCMA GEO, 2024 ISN announcement and Ross Gale industry coverage; dated claims</t>
-        </is>
-      </c>
+          <t>The leading manufacturers in IPP's chemical process inventory, ranked by their IMS manufacturer-filter presence, each with its product families and a link to that maker's IMS listings, followed by the two IPP group companies.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>li</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAQs</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Preserve three key original answers; definition link, price factors, buying, selling, shipping questions</t>
-        </is>
-      </c>
+          <t>Pfaudler: glass-lined reactors, tanks and agitators</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>li</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chemical Process Plants Resources</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Six relevant resource links; no latest-posts feed</t>
-        </is>
-      </c>
+          <t>De Dietrich: glass-lined reactors and tanks</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alfa Laval: heat exchangers and centrifuges</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Krauss Maffei: centrifuges</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Westfalia: centrifuges</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gale Process Solutions: new stainless steel equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Universal Glasteel Equipment: new and re-glassed glass-lined equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Find the right plant or equipment for your project</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Content type: sourced commercial copy. State each owned attribute once with its value. Contact, phone and inventory destinations</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Why chemical manufacturers choose IPP for chemical process plants</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Five advantage cards with the original labels, each stating one or two attributes with their values: release dates per stock number; maker and plant-line breadth; offices in 15 countries and 160,000+ customers; operating-plant provenance and available records; the approved capital and lead-time line. A closing note names GPS and UGE for new equipment.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Immediate availability</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Massive selection</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Global access</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Validation-ready</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cost efficiency</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Advantage card: one or two attribute statements with values.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>What do chemical manufacturers say about IPP?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Introduces IPP's customer video interview series and links the playlist.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>How buying from IPP works</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Locked by the user: the five steps and their copy stay as published on the review page.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Share your requirements</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Review specifications and inspect</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agree the purchase scope</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Plan dismantling and relocation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Arrange shipping and start-up support</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Locked step copy.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sell chemical plants and surplus equipment to IPP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seller path in the same arrangement as the buyer steps. The intro states what IPP acquires (complete plant sites with land, buildings, equipment and intellectual property; process units and lines; individual surplus equipment), the site states it handles, who sells to IPP and the seller outcomes. Four steps follow, then the sell-a-plant and sell-equipment forms.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Send your asset information</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Seller step: the asset list, photographs, plant location, available documents and removal deadline.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IPP values the assets</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Seller step: IPP reviews the information, visits the site where needed and values the assets for acquisition or for marketing to its global buyer network.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Agree the sale structure</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seller step: IPP acquires the assets outright on an as-is, where-is basis or markets them to its buyer network; a complete site can include land, buildings, equipment and intellectual property.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Decommissioning, dismantling and removal</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seller step: IPP handles decommissioning, dismantling coordination, packaging, freight and export, and works with the owner's EHS team on permit closure, emissions and utility shutoffs.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Industries we serve</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>The six original sectors as bare labels, after a one-line lead-in naming IPP's role on both sides of the market.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Petrochemicals</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Polymers and plastics</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Solvents, resins and adhesives</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Acids, amines and surfactants</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agrochemicals and specialty chemicals</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Global inventory. Local support.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Company-owned warehouses and workshops in Eastover (South Carolina), Billingham (England) and Bitterfeld-Wolfen (Germany) with their published addresses; offices in 15 countries; asset location confirmed with each quotation.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Eastover, South Carolina</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Address card.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Billingham, England</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Address card.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bitterfeld-Wolfen</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Address card.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chemical plant projects and industry recognition</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dated, linked proof of IPP's chemical plant work on both sides: plant marketing for BASF at Ludwigshafen (May 2024); the Novartis Grimsby API site acquisition by affiliate Humber Industrials; the CDMO API equipment relocation to Eastover; decommissioning credentials and the Nuol Green Chemistry site transfer; Ross Gale's Chemical Engineering article (December 2024).</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Marketing major chemical plants</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Repurposing a pharmaceutical site</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Moving assets into their next use</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Decommissioning and site transfer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Project card: one dated, sourced statement.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chemical Process Plants Resources</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tabbed resources container with About Us, FAQs and Blog panels.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Used chemical process plants and equipment from IPP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Company profile in short statements: headquarters address; offices in 15 named countries and 160,000+ customers; chemical inventory scope and sourcing; the GPS and UGE group companies; dated projects; Ross Gale's article. Team photo beside the text.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Used chemical process plant FAQs</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Fourteen answer-first FAQs: nine for buyers, three of them preserved word for word, and five for sellers. Each answer opens with the verdict or value, adds one supporting fact and ends with the next action where one exists.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Does IPP offer full chemical plants for sale?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Can I inspect the equipment before buying?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Where does IPP source its chemical equipment?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>What is chemical process plant equipment?</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>How do I get a price for a chemical plant or equipment?</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Can IPP help with international shipping?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>What documentation is available for a used plant?</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Is financing available?</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Does IPP sell new chemical process equipment?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Does IPP buy shutdown chemical plants and surplus equipment?</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>What information should I provide when selling?</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Does IPP buy the land and buildings with a chemical plant?</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Does IPP assume environmental obligations at a plant site?</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>What happens to a chemical plant site after a sale?</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FAQ answer: verdict or value first, one supporting fact, next action.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Chemical process plant articles</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Six article cards from the Related articles sheet: five buyer guides and one seller article.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ready to buy or sell chemical plants and equipment?</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Closing actions for both sides: buyers send process, capacity and destination; sellers send their asset list. Contact link, phone, email and the Princeton Junction headquarters address, plus the sell-a-plant and sell-equipment forms.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -968,8 +2822,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1039,24 +2893,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/chemical-process-plant-equipment-used-systems-for-sale/</t>
+          <t>/used-chemical-process-plants-for-sale/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Used Chemical Process Plants for Sale | IPP</t>
+          <t>Used Chemical Process Plants for Sale</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Explore used chemical process plants, complete lines and equipment from IPP. View specifications, arrange inspections, or sell your surplus chemical assets.</t>
+          <t>Home / Process plants / Chemical plants &amp;amp; equipment Complete plants. Process lines. Individual equipment.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1070,7 +2924,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>In-session; approved existing URL</t>
+          <t>fallback</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
